--- a/samples/TENDER_TEMPLATE.xlsx
+++ b/samples/TENDER_TEMPLATE.xlsx
@@ -1,57 +1,170 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tender Information" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance Tracker" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tender Information" sheetId="1" r:id="rId1"/>
+    <sheet name="Compliance Tracker" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>TENDER INFORMATION</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>Submission Deadline</t>
+  </si>
+  <si>
+    <t>Purchase Item</t>
+  </si>
+  <si>
+    <t>Issued By</t>
+  </si>
+  <si>
+    <t>Requesting Dept</t>
+  </si>
+  <si>
+    <t>Tender Reference</t>
+  </si>
+  <si>
+    <t>Procurement Type</t>
+  </si>
+  <si>
+    <t>Estimated Value</t>
+  </si>
+  <si>
+    <t>Purchase Category</t>
+  </si>
+  <si>
+    <t>IT PROCUREMENT COMPLIANCE TRACKER</t>
+  </si>
+  <si>
+    <t>Seq</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>M/O</t>
+  </si>
+  <si>
+    <t>Vendor Status</t>
+  </si>
+  <si>
+    <t>Vendor Remarks</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="14"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="9.5"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1B3A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9A84C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF0E3460"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F7"/>
+        <bgColor rgb="FFEEF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0FE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -59,89 +172,595 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9.5"/>
+        <color rgb="FF1A1A1A"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE8F0FE"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCCCCCC"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCCCCCC"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC9A84C"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCCCCCC"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCCCCCC"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DE9F14E-9A5B-4784-8587-395BDCAE2559}" name="TenderRequirements" displayName="TenderRequirements" ref="A2:G3" insertRow="1" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A2:G3" xr:uid="{2DE9F14E-9A5B-4784-8587-395BDCAE2559}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{6134FB54-7724-4EBD-A07F-18A0CCB323E3}" name="Seq" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{98D096A9-B4CB-48B4-AF79-90A64E13463F}" name="Ref" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{4C875D68-7DDD-4B86-BF11-86C288AA3BEF}" name="Section" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{B383D702-5879-4365-9CD4-36B92199D270}" name="Requirement" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{48ABCBE4-D4D9-4A41-8770-66288EAAC8B3}" name="M/O" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{6A59D70C-1821-480F-B3AE-CD394C645BD8}" name="Vendor Status" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{74608B87-EFCA-4DFD-9AA8-0B2A36596174}" name="Vendor Remarks" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,156 +1047,277 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2210E0C5-1DBD-40F3-A5D4-F3CDAFA185FE}">
+  <dimension ref="A1:S53"/>
+  <sheetFormatPr defaultRowHeight="23.25" customHeight="1"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="50.5703125" style="15" customWidth="1"/>
+    <col min="3" max="19" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TENDER INFORMATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Issue Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Submission Deadline</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Purchase Item</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Issued By</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Requesting Dept</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Tender Reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Procurement Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Estimated Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Purchase Category</t>
-        </is>
-      </c>
+    <row r="1" spans="1:2" ht="33" customHeight="1">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+    </row>
+    <row r="3" spans="1:2" ht="27.75" customHeight="1">
+      <c r="A3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11"/>
+    </row>
+    <row r="4" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12"/>
+    </row>
+    <row r="5" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12"/>
+    </row>
+    <row r="6" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12"/>
+    </row>
+    <row r="7" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12"/>
+    </row>
+    <row r="8" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12"/>
+    </row>
+    <row r="9" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12"/>
+    </row>
+    <row r="10" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13"/>
+    </row>
+    <row r="11" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B11" s="14"/>
+    </row>
+    <row r="12" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B12" s="14"/>
+    </row>
+    <row r="13" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B13" s="14"/>
+    </row>
+    <row r="14" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B14" s="14"/>
+    </row>
+    <row r="15" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B15" s="14"/>
+    </row>
+    <row r="16" spans="1:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B16" s="14"/>
+    </row>
+    <row r="17" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B17" s="14"/>
+    </row>
+    <row r="18" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B18" s="14"/>
+    </row>
+    <row r="19" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B19" s="14"/>
+    </row>
+    <row r="20" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B20" s="14"/>
+    </row>
+    <row r="21" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B21" s="14"/>
+    </row>
+    <row r="22" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B22" s="14"/>
+    </row>
+    <row r="23" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B23" s="14"/>
+    </row>
+    <row r="24" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B24" s="14"/>
+    </row>
+    <row r="25" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B25" s="14"/>
+    </row>
+    <row r="26" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B26" s="14"/>
+    </row>
+    <row r="27" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B27" s="14"/>
+    </row>
+    <row r="28" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B28" s="14"/>
+    </row>
+    <row r="29" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B29" s="14"/>
+    </row>
+    <row r="30" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B30" s="14"/>
+    </row>
+    <row r="31" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B31" s="14"/>
+    </row>
+    <row r="32" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B32" s="14"/>
+    </row>
+    <row r="33" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B33" s="14"/>
+    </row>
+    <row r="34" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B34" s="14"/>
+    </row>
+    <row r="35" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B35" s="14"/>
+    </row>
+    <row r="36" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B36" s="14"/>
+    </row>
+    <row r="37" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B37" s="14"/>
+    </row>
+    <row r="38" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B38" s="14"/>
+    </row>
+    <row r="39" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B39" s="14"/>
+    </row>
+    <row r="40" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B40" s="14"/>
+    </row>
+    <row r="41" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B41" s="14"/>
+    </row>
+    <row r="42" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B42" s="14"/>
+    </row>
+    <row r="43" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B43" s="14"/>
+    </row>
+    <row r="44" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B44" s="14"/>
+    </row>
+    <row r="45" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B45" s="14"/>
+    </row>
+    <row r="46" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B46" s="14"/>
+    </row>
+    <row r="47" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B47" s="14"/>
+    </row>
+    <row r="48" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B48" s="14"/>
+    </row>
+    <row r="49" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B49" s="14"/>
+    </row>
+    <row r="50" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B50" s="14"/>
+    </row>
+    <row r="51" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B51" s="14"/>
+    </row>
+    <row r="52" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B52" s="14"/>
+    </row>
+    <row r="53" spans="2:2" s="10" customFormat="1" ht="23.25" customHeight="1">
+      <c r="B53" s="14"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="65.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>IT PROCUREMENT COMPLIANCE TRACKER</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Seq</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>M/O</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Vendor Status</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Vendor Remarks</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="27.95" customHeight="1">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="27.95" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>